--- a/Assets/Game/Content/Data/BuffTable.xlsx
+++ b/Assets/Game/Content/Data/BuffTable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlier\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DC453E-CA35-4CB7-AC55-7A4FCE7653E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE0A7B1-7687-4F78-A19B-DACF5121FD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>Id</t>
   </si>
@@ -129,75 +129,91 @@
     <t>Calm</t>
   </si>
   <si>
+    <t>Rusted</t>
+  </si>
+  <si>
+    <t>Buff_Rusted</t>
+  </si>
+  <si>
+    <t>Buff_Rusted_Desc</t>
+  </si>
+  <si>
+    <t>Buff/Buff.Rust</t>
+  </si>
+  <si>
+    <t>HighReactivity</t>
+  </si>
+  <si>
+    <t>Buff_HighReactivity</t>
+  </si>
+  <si>
+    <t>Buff_HighReactivity_Desc</t>
+  </si>
+  <si>
+    <t>Buff/Buff.Activity</t>
+  </si>
+  <si>
+    <t>Sturdy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Calm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Sturdy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Calm_Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Sturdy_Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reflect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Buff/Buff.Calm</t>
-  </si>
-  <si>
-    <t>Rusted</t>
-  </si>
-  <si>
-    <t>Buff_Rusted</t>
-  </si>
-  <si>
-    <t>Buff_Rusted_Desc</t>
-  </si>
-  <si>
-    <t>Buff/Buff.Rust</t>
-  </si>
-  <si>
-    <t>HighReactivity</t>
-  </si>
-  <si>
-    <t>Buff_HighReactivity</t>
-  </si>
-  <si>
-    <t>Buff_HighReactivity_Desc</t>
-  </si>
-  <si>
-    <t>Buff/Buff.Activity</t>
-  </si>
-  <si>
-    <t>Sturdy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Calm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Sturdy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Calm_Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Sturdy_Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reflect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Reflect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff/Buff.Sturdy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff/Buff.Reflect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -236,9 +252,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,13 +534,13 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="59.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.8984375" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" customWidth="1"/>
+    <col min="3" max="3" width="59.3984375" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" customWidth="1"/>
+    <col min="5" max="5" width="16.796875" customWidth="1"/>
+    <col min="6" max="6" width="14.3984375" customWidth="1"/>
+    <col min="7" max="7" width="11.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -692,10 +709,10 @@
         <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>99</v>
@@ -706,19 +723,19 @@
       <c r="F8" t="b">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
-        <v>32</v>
+      <c r="G8" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9">
         <v>99</v>
@@ -729,19 +746,19 @@
       <c r="F9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
-        <v>19</v>
+      <c r="G9" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D10">
         <v>99</v>
@@ -752,19 +769,19 @@
       <c r="F10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
-        <v>19</v>
+      <c r="G10" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
       </c>
       <c r="D12">
         <v>99</v>
@@ -776,18 +793,18 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
       </c>
       <c r="D13">
         <v>999</v>
@@ -799,14 +816,14 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>